--- a/Assets/Project/Csv/Items.xlsx
+++ b/Assets/Project/Csv/Items.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\GitLab\Dairy Farm\Assets\Project\Csv\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8044ABF5-2EC6-4962-9B9F-BC4336F4E158}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CDFB509-D9F8-4AC8-87AC-C4D0E0632AD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{60FB3A8B-F729-4DB7-8913-C0C73234401C}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="ExternalData_1" localSheetId="0" hidden="1">Item!$A$1:$C$5</definedName>
+    <definedName name="ExternalData_1" localSheetId="0" hidden="1">Item!$A$1:$C$9</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
   <si>
     <t>index</t>
   </si>
@@ -85,6 +85,38 @@
   </si>
   <si>
     <t xml:space="preserve"> 씨앗을 심어 쌀를 수확 할 수 있다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>수확한 쌀을 쌀가마니에 모았다</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>쌀 1가마</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>토마토</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>맛있게 여물은 토마토다</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>호박</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>속이 꽉찬 호박이다, 할로윈에 쓸만해 보인다</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>딸기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>빨간 딸기가 맛있어보인다</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -131,8 +163,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -172,8 +207,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{418F368F-02FE-42D4-9FFE-25BC2E195B7B}" name="Item" displayName="Item" ref="A1:C5" tableType="queryTable" totalsRowShown="0">
-  <autoFilter ref="A1:C5" xr:uid="{418F368F-02FE-42D4-9FFE-25BC2E195B7B}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{418F368F-02FE-42D4-9FFE-25BC2E195B7B}" name="Item" displayName="Item" ref="A1:C9" tableType="queryTable" totalsRowShown="0">
+  <autoFilter ref="A1:C9" xr:uid="{418F368F-02FE-42D4-9FFE-25BC2E195B7B}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{05660362-4482-41B7-95EB-8748141CBDCD}" uniqueName="1" name="index" queryTableFieldId="1"/>
     <tableColumn id="2" xr3:uid="{67B3F1B1-5639-4264-A911-322BE74919F5}" uniqueName="2" name=" nameTag" queryTableFieldId="2" dataDxfId="1"/>
@@ -500,12 +535,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1B397A7-A3F0-4E6D-A17E-50C723D637EC}">
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="37" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="41.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
@@ -532,7 +567,7 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3">
-        <v>2</v>
+        <v>101</v>
       </c>
       <c r="B3" t="s">
         <v>8</v>
@@ -543,7 +578,7 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4">
-        <v>3</v>
+        <v>201</v>
       </c>
       <c r="B4" t="s">
         <v>7</v>
@@ -554,13 +589,57 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5">
-        <v>4</v>
+        <v>301</v>
       </c>
       <c r="B5" t="s">
         <v>9</v>
       </c>
       <c r="C5" t="s">
         <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>1001</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>1101</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>1201</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>1301</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Project/Csv/Items.xlsx
+++ b/Assets/Project/Csv/Items.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\GitLab\Dairy Farm\Assets\Project\Csv\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CDFB509-D9F8-4AC8-87AC-C4D0E0632AD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB9A9236-E922-4B72-89C1-B20D06743D9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{60FB3A8B-F729-4DB7-8913-C0C73234401C}"/>
+    <workbookView xWindow="1455" yWindow="2775" windowWidth="21600" windowHeight="11295" xr2:uid="{60FB3A8B-F729-4DB7-8913-C0C73234401C}"/>
   </bookViews>
   <sheets>
     <sheet name="Item" sheetId="2" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
   <si>
     <t>index</t>
   </si>
@@ -117,6 +117,18 @@
   </si>
   <si>
     <t>빨간 딸기가 맛있어보인다</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>maxStack</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>maxDurability</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sellPrice</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -163,11 +175,8 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -196,23 +205,29 @@
 
 <file path=xl/queryTables/queryTable1.xml><?xml version="1.0" encoding="utf-8"?>
 <queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="ExternalData_1" connectionId="1" xr16:uid="{122D487E-01D7-405F-AFCF-8E2E17875C6B}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0">
-  <queryTableRefresh nextId="4">
-    <queryTableFields count="3">
+  <queryTableRefresh nextId="7" unboundColumnsRight="3">
+    <queryTableFields count="6">
       <queryTableField id="1" name="index" tableColumnId="1"/>
       <queryTableField id="2" name=" nameTag" tableColumnId="2"/>
       <queryTableField id="3" name=" description" tableColumnId="3"/>
+      <queryTableField id="4" dataBound="0" tableColumnId="4"/>
+      <queryTableField id="5" dataBound="0" tableColumnId="5"/>
+      <queryTableField id="6" dataBound="0" tableColumnId="6"/>
     </queryTableFields>
   </queryTableRefresh>
 </queryTable>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{418F368F-02FE-42D4-9FFE-25BC2E195B7B}" name="Item" displayName="Item" ref="A1:C9" tableType="queryTable" totalsRowShown="0">
-  <autoFilter ref="A1:C9" xr:uid="{418F368F-02FE-42D4-9FFE-25BC2E195B7B}"/>
-  <tableColumns count="3">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{418F368F-02FE-42D4-9FFE-25BC2E195B7B}" name="Item" displayName="Item" ref="A1:F9" tableType="queryTable" totalsRowShown="0">
+  <autoFilter ref="A1:F9" xr:uid="{418F368F-02FE-42D4-9FFE-25BC2E195B7B}"/>
+  <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{05660362-4482-41B7-95EB-8748141CBDCD}" uniqueName="1" name="index" queryTableFieldId="1"/>
     <tableColumn id="2" xr3:uid="{67B3F1B1-5639-4264-A911-322BE74919F5}" uniqueName="2" name=" nameTag" queryTableFieldId="2" dataDxfId="1"/>
     <tableColumn id="3" xr3:uid="{1167E9E5-5F7E-4776-A93E-FF991DA08CB1}" uniqueName="3" name=" description" queryTableFieldId="3" dataDxfId="0"/>
+    <tableColumn id="4" xr3:uid="{70F0AD17-D228-4D81-A4E3-DE03FB35DFF6}" uniqueName="4" name="maxStack" queryTableFieldId="4"/>
+    <tableColumn id="5" xr3:uid="{83466E01-A881-480E-8441-C5C61DAD06CC}" uniqueName="5" name="maxDurability" queryTableFieldId="5"/>
+    <tableColumn id="6" xr3:uid="{803666EB-622A-4274-B851-4195F2EAD4C2}" uniqueName="6" name="sellPrice" queryTableFieldId="6"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -535,7 +550,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1B397A7-A3F0-4E6D-A17E-50C723D637EC}">
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.5" bestFit="1" customWidth="1"/>
@@ -543,7 +558,7 @@
     <col min="3" max="3" width="41.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -553,8 +568,17 @@
       <c r="C1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -564,8 +588,17 @@
       <c r="C2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D2">
+        <v>99</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>101</v>
       </c>
@@ -575,8 +608,17 @@
       <c r="C3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D3">
+        <v>99</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>201</v>
       </c>
@@ -586,8 +628,17 @@
       <c r="C4" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D4">
+        <v>99</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>301</v>
       </c>
@@ -597,49 +648,94 @@
       <c r="C5" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D5">
+        <v>99</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>1001</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D6">
+        <v>99</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>1101</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" t="s">
         <v>13</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C7" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D7">
+        <v>99</v>
+      </c>
+      <c r="E7">
+        <v>1</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>1201</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B8" t="s">
         <v>15</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="C8" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D8">
+        <v>99</v>
+      </c>
+      <c r="E8">
+        <v>1</v>
+      </c>
+      <c r="F8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>1301</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B9" t="s">
         <v>17</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="C9" t="s">
         <v>18</v>
+      </c>
+      <c r="D9">
+        <v>99</v>
+      </c>
+      <c r="E9">
+        <v>1</v>
+      </c>
+      <c r="F9">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
